--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20222.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20222.xlsx
@@ -661,16 +661,19 @@
         <v>28</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>28</v>
       </c>
-      <c r="E2">
-        <v>28</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -684,16 +687,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>92.86</v>
+      </c>
+      <c r="H3">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -707,16 +713,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="H4">
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -730,16 +739,19 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>92.86</v>
+      </c>
+      <c r="H5">
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -753,16 +765,19 @@
         <v>20</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="H6">
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -827,7 +842,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -844,16 +859,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>96.43000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -870,16 +885,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -896,16 +911,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>71.43000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -922,16 +937,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20222.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -88,10 +88,25 @@
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>MARIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
   </si>
 </sst>
 </file>
@@ -833,13 +848,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H2">
         <v>8.300000000000001</v>
@@ -859,16 +874,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>92.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -885,16 +900,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -920,7 +935,7 @@
         <v>92.86</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -946,7 +961,7 @@
         <v>90</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -956,7 +971,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -994,10 +1009,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1006,6 +1021,52 @@
         <v>13</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920340</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920354</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20222.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20222.xlsx
@@ -85,28 +85,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CUEVAS</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>CUEVAS</t>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
   </si>
   <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>JAHEL</t>
   </si>
   <si>
     <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>JAHEL</t>
   </si>
 </sst>
 </file>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920152</v>
+        <v>20330051920340</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -1015,10 +1015,10 @@
         <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920340</v>
+        <v>20330051920354</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1049,10 +1049,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920354</v>
+        <v>20330051920152</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
@@ -1061,13 +1061,13 @@
         <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
